--- a/Database_Saved_Cases.xlsx
+++ b/Database_Saved_Cases.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L402"/>
+  <dimension ref="A1:O402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,12 +463,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Survey Fee</t>
+          <t>Total Survey Fee</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Rental</t>
+          <t>Rental Per Day</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -478,7 +478,22 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Rental Fee</t>
+          <t>Total Rental</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Survey Fees</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Photographs Cost</t>
         </is>
       </c>
     </row>
@@ -525,6 +540,9 @@
       <c r="L2" t="n">
         <v>960</v>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -569,6 +587,9 @@
       <c r="L3" t="n">
         <v>1440</v>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -613,6 +634,9 @@
       <c r="L4" t="n">
         <v>1440</v>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -657,6 +681,9 @@
       <c r="L5" t="n">
         <v>900</v>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -701,6 +728,9 @@
       <c r="L6" t="n">
         <v>1260</v>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -745,6 +775,9 @@
       <c r="L7" t="n">
         <v>1560</v>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -789,6 +822,9 @@
       <c r="L8" t="n">
         <v>1680</v>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -833,6 +869,9 @@
       <c r="L9" t="n">
         <v>1080</v>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -877,6 +916,9 @@
       <c r="L10" t="n">
         <v>720</v>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -921,6 +963,9 @@
       <c r="L11" t="n">
         <v>1080</v>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -965,6 +1010,9 @@
       <c r="L12" t="n">
         <v>1080</v>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1009,6 +1057,9 @@
       <c r="L13" t="n">
         <v>1560</v>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1053,6 +1104,9 @@
       <c r="L14" t="n">
         <v>2880</v>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1097,6 +1151,9 @@
       <c r="L15" t="n">
         <v>3240</v>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1141,6 +1198,9 @@
       <c r="L16" t="n">
         <v>840</v>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1185,6 +1245,9 @@
       <c r="L17" t="n">
         <v>2160</v>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1229,6 +1292,9 @@
       <c r="L18" t="n">
         <v>1080</v>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1273,6 +1339,9 @@
       <c r="L19" t="n">
         <v>900</v>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1317,6 +1386,9 @@
       <c r="L20" t="n">
         <v>1200</v>
       </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1361,6 +1433,9 @@
       <c r="L21" t="n">
         <v>1200</v>
       </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1405,6 +1480,9 @@
       <c r="L22" t="n">
         <v>840</v>
       </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1449,6 +1527,9 @@
       <c r="L23" t="n">
         <v>720</v>
       </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1493,6 +1574,9 @@
       <c r="L24" t="n">
         <v>840</v>
       </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1537,6 +1621,9 @@
       <c r="L25" t="n">
         <v>1200</v>
       </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1581,6 +1668,9 @@
       <c r="L26" t="n">
         <v>960</v>
       </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1625,6 +1715,9 @@
       <c r="L27" t="n">
         <v>900</v>
       </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1669,6 +1762,9 @@
       <c r="L28" t="n">
         <v>1080</v>
       </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1713,6 +1809,9 @@
       <c r="L29" t="n">
         <v>960</v>
       </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1757,6 +1856,9 @@
       <c r="L30" t="n">
         <v>720</v>
       </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1801,6 +1903,9 @@
       <c r="L31" t="n">
         <v>1440</v>
       </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1845,6 +1950,9 @@
       <c r="L32" t="n">
         <v>720</v>
       </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1889,6 +1997,9 @@
       <c r="L33" t="n">
         <v>840</v>
       </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1933,6 +2044,9 @@
       <c r="L34" t="n">
         <v>600</v>
       </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1977,6 +2091,9 @@
       <c r="L35" t="n">
         <v>2160</v>
       </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2021,6 +2138,9 @@
       <c r="L36" t="n">
         <v>720</v>
       </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2065,6 +2185,9 @@
       <c r="L37" t="n">
         <v>1800</v>
       </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2109,6 +2232,9 @@
       <c r="L38" t="n">
         <v>720</v>
       </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2153,6 +2279,9 @@
       <c r="L39" t="n">
         <v>720</v>
       </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2197,6 +2326,9 @@
       <c r="L40" t="n">
         <v>1980</v>
       </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2241,6 +2373,9 @@
       <c r="L41" t="n">
         <v>1320</v>
       </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2285,6 +2420,9 @@
       <c r="L42" t="n">
         <v>2400</v>
       </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2329,6 +2467,9 @@
       <c r="L43" t="n">
         <v>840</v>
       </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2373,6 +2514,9 @@
       <c r="L44" t="n">
         <v>1800</v>
       </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2417,6 +2561,9 @@
       <c r="L45" t="n">
         <v>1200</v>
       </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2461,6 +2608,9 @@
       <c r="L46" t="n">
         <v>1080</v>
       </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2505,6 +2655,9 @@
       <c r="L47" t="n">
         <v>720</v>
       </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2549,6 +2702,9 @@
       <c r="L48" t="n">
         <v>1800</v>
       </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2593,6 +2749,9 @@
       <c r="L49" t="n">
         <v>960</v>
       </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2637,6 +2796,9 @@
       <c r="L50" t="n">
         <v>480</v>
       </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2681,6 +2843,9 @@
       <c r="L51" t="n">
         <v>720</v>
       </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2725,6 +2890,9 @@
       <c r="L52" t="n">
         <v>1260</v>
       </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2769,6 +2937,9 @@
       <c r="L53" t="n">
         <v>840</v>
       </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2813,6 +2984,9 @@
       <c r="L54" t="n">
         <v>2880</v>
       </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2857,6 +3031,9 @@
       <c r="L55" t="n">
         <v>840</v>
       </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2901,6 +3078,9 @@
       <c r="L56" t="n">
         <v>840</v>
       </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2945,6 +3125,9 @@
       <c r="L57" t="n">
         <v>1320</v>
       </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2989,6 +3172,9 @@
       <c r="L58" t="n">
         <v>840</v>
       </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3033,6 +3219,9 @@
       <c r="L59" t="n">
         <v>1200</v>
       </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3077,6 +3266,9 @@
       <c r="L60" t="n">
         <v>3600</v>
       </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3121,6 +3313,9 @@
       <c r="L61" t="n">
         <v>1080</v>
       </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3165,6 +3360,9 @@
       <c r="L62" t="n">
         <v>2520</v>
       </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3209,6 +3407,9 @@
       <c r="L63" t="n">
         <v>1200</v>
       </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3253,6 +3454,9 @@
       <c r="L64" t="n">
         <v>2160</v>
       </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3297,6 +3501,9 @@
       <c r="L65" t="n">
         <v>960</v>
       </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3341,6 +3548,9 @@
       <c r="L66" t="n">
         <v>2160</v>
       </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3385,6 +3595,9 @@
       <c r="L67" t="n">
         <v>1260</v>
       </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3429,6 +3642,9 @@
       <c r="L68" t="n">
         <v>1440</v>
       </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3471,6 +3687,9 @@
       <c r="L69" t="n">
         <v>1920</v>
       </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3515,6 +3734,9 @@
       <c r="L70" t="n">
         <v>1620</v>
       </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3559,6 +3781,9 @@
       <c r="L71" t="n">
         <v>960</v>
       </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3603,6 +3828,9 @@
       <c r="L72" t="n">
         <v>960</v>
       </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3647,6 +3875,9 @@
       <c r="L73" t="n">
         <v>3240</v>
       </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3691,6 +3922,9 @@
       <c r="L74" t="n">
         <v>720</v>
       </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3735,6 +3969,9 @@
       <c r="L75" t="n">
         <v>2160</v>
       </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -3779,6 +4016,9 @@
       <c r="L76" t="n">
         <v>1920</v>
       </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -3823,6 +4063,9 @@
       <c r="L77" t="n">
         <v>1080</v>
       </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -3867,6 +4110,9 @@
       <c r="L78" t="n">
         <v>1800</v>
       </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -3911,6 +4157,9 @@
       <c r="L79" t="n">
         <v>1200</v>
       </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -3955,6 +4204,9 @@
       <c r="L80" t="n">
         <v>1260</v>
       </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -3999,6 +4251,9 @@
       <c r="L81" t="n">
         <v>960</v>
       </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4043,6 +4298,9 @@
       <c r="L82" t="n">
         <v>600</v>
       </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4087,6 +4345,9 @@
       <c r="L83" t="n">
         <v>600</v>
       </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4131,6 +4392,9 @@
       <c r="L84" t="n">
         <v>1260</v>
       </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4175,6 +4439,9 @@
       <c r="L85" t="n">
         <v>900</v>
       </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4219,6 +4486,9 @@
       <c r="L86" t="n">
         <v>840</v>
       </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4263,6 +4533,9 @@
       <c r="L87" t="n">
         <v>720</v>
       </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4307,6 +4580,9 @@
       <c r="L88" t="n">
         <v>2160</v>
       </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4351,6 +4627,9 @@
       <c r="L89" t="n">
         <v>2700</v>
       </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4395,6 +4674,9 @@
       <c r="L90" t="n">
         <v>480</v>
       </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4439,6 +4721,9 @@
       <c r="L91" t="n">
         <v>1080</v>
       </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4483,6 +4768,9 @@
       <c r="L92" t="n">
         <v>1440</v>
       </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4527,6 +4815,9 @@
       <c r="L93" t="n">
         <v>1620</v>
       </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4571,6 +4862,9 @@
       <c r="L94" t="n">
         <v>1080</v>
       </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4615,6 +4909,9 @@
       <c r="L95" t="n">
         <v>900</v>
       </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4659,6 +4956,9 @@
       <c r="L96" t="n">
         <v>1260</v>
       </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4703,6 +5003,9 @@
       <c r="L97" t="n">
         <v>1920</v>
       </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -4747,6 +5050,9 @@
       <c r="L98" t="n">
         <v>480</v>
       </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -4791,6 +5097,9 @@
       <c r="L99" t="n">
         <v>1440</v>
       </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -4835,6 +5144,9 @@
       <c r="L100" t="n">
         <v>1080</v>
       </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -4879,6 +5191,9 @@
       <c r="L101" t="n">
         <v>2160</v>
       </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -4923,6 +5238,9 @@
       <c r="L102" t="n">
         <v>1260</v>
       </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4967,6 +5285,9 @@
       <c r="L103" t="n">
         <v>1260</v>
       </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5011,6 +5332,9 @@
       <c r="L104" t="n">
         <v>720</v>
       </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5055,6 +5379,9 @@
       <c r="L105" t="n">
         <v>2160</v>
       </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5099,6 +5426,9 @@
       <c r="L106" t="n">
         <v>2160</v>
       </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5143,6 +5473,9 @@
       <c r="L107" t="n">
         <v>1080</v>
       </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5187,6 +5520,9 @@
       <c r="L108" t="n">
         <v>1080</v>
       </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5231,6 +5567,9 @@
       <c r="L109" t="n">
         <v>1440</v>
       </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5275,6 +5614,9 @@
       <c r="L110" t="n">
         <v>600</v>
       </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5319,6 +5661,9 @@
       <c r="L111" t="n">
         <v>720</v>
       </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5363,6 +5708,9 @@
       <c r="L112" t="n">
         <v>720</v>
       </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5407,6 +5755,9 @@
       <c r="L113" t="n">
         <v>1200</v>
       </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5451,6 +5802,9 @@
       <c r="L114" t="n">
         <v>720</v>
       </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5495,6 +5849,9 @@
       <c r="L115" t="n">
         <v>360</v>
       </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5539,6 +5896,9 @@
       <c r="L116" t="n">
         <v>2700</v>
       </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5583,6 +5943,9 @@
       <c r="L117" t="n">
         <v>2160</v>
       </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -5627,6 +5990,9 @@
       <c r="L118" t="n">
         <v>960</v>
       </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -5671,6 +6037,9 @@
       <c r="L119" t="n">
         <v>720</v>
       </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -5715,6 +6084,9 @@
       <c r="L120" t="n">
         <v>1080</v>
       </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -5759,6 +6131,9 @@
       <c r="L121" t="n">
         <v>720</v>
       </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -5803,6 +6178,9 @@
       <c r="L122" t="n">
         <v>720</v>
       </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5847,6 +6225,9 @@
       <c r="L123" t="n">
         <v>900</v>
       </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -5891,6 +6272,9 @@
       <c r="L124" t="n">
         <v>840</v>
       </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -5935,6 +6319,9 @@
       <c r="L125" t="n">
         <v>1260</v>
       </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -5979,6 +6366,9 @@
       <c r="L126" t="n">
         <v>2160</v>
       </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6023,6 +6413,9 @@
       <c r="L127" t="n">
         <v>2520</v>
       </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6067,6 +6460,9 @@
       <c r="L128" t="n">
         <v>1800</v>
       </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6111,6 +6507,9 @@
       <c r="L129" t="n">
         <v>1260</v>
       </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6155,6 +6554,9 @@
       <c r="L130" t="n">
         <v>600</v>
       </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6199,6 +6601,9 @@
       <c r="L131" t="n">
         <v>900</v>
       </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6243,6 +6648,9 @@
       <c r="L132" t="n">
         <v>720</v>
       </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6287,6 +6695,9 @@
       <c r="L133" t="n">
         <v>960</v>
       </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6331,6 +6742,9 @@
       <c r="L134" t="n">
         <v>1620</v>
       </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6375,6 +6789,9 @@
       <c r="L135" t="n">
         <v>4680</v>
       </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6419,6 +6836,9 @@
       <c r="L136" t="n">
         <v>600</v>
       </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6463,6 +6883,9 @@
       <c r="L137" t="n">
         <v>1080</v>
       </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6507,6 +6930,9 @@
       <c r="L138" t="n">
         <v>720</v>
       </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6551,6 +6977,9 @@
       <c r="L139" t="n">
         <v>1080</v>
       </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -6595,6 +7024,9 @@
       <c r="L140" t="n">
         <v>720</v>
       </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -6639,6 +7071,9 @@
       <c r="L141" t="n">
         <v>1440</v>
       </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -6683,6 +7118,9 @@
       <c r="L142" t="n">
         <v>720</v>
       </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -6727,6 +7165,9 @@
       <c r="L143" t="n">
         <v>1800</v>
       </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -6771,6 +7212,9 @@
       <c r="L144" t="n">
         <v>840</v>
       </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -6815,6 +7259,9 @@
       <c r="L145" t="n">
         <v>720</v>
       </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -6859,6 +7306,9 @@
       <c r="L146" t="n">
         <v>1620</v>
       </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -6903,6 +7353,9 @@
       <c r="L147" t="n">
         <v>1800</v>
       </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -6947,6 +7400,9 @@
       <c r="L148" t="n">
         <v>900</v>
       </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -6991,6 +7447,9 @@
       <c r="L149" t="n">
         <v>3600</v>
       </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7035,6 +7494,9 @@
       <c r="L150" t="n">
         <v>1260</v>
       </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7077,6 +7539,9 @@
       <c r="L151" t="n">
         <v>0</v>
       </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7121,6 +7586,9 @@
       <c r="L152" t="n">
         <v>900</v>
       </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7165,6 +7633,9 @@
       <c r="L153" t="n">
         <v>1260</v>
       </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7209,6 +7680,9 @@
       <c r="L154" t="n">
         <v>1200</v>
       </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7253,6 +7727,9 @@
       <c r="L155" t="n">
         <v>900</v>
       </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7297,6 +7774,9 @@
       <c r="L156" t="n">
         <v>720</v>
       </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7341,6 +7821,9 @@
       <c r="L157" t="n">
         <v>840</v>
       </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7385,6 +7868,9 @@
       <c r="L158" t="n">
         <v>2040</v>
       </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7429,6 +7915,9 @@
       <c r="L159" t="n">
         <v>720</v>
       </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7473,6 +7962,9 @@
       <c r="L160" t="n">
         <v>1080</v>
       </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -7517,6 +8009,9 @@
       <c r="L161" t="n">
         <v>720</v>
       </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -7561,6 +8056,9 @@
       <c r="L162" t="n">
         <v>840</v>
       </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -7605,6 +8103,9 @@
       <c r="L163" t="n">
         <v>1920</v>
       </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -7649,6 +8150,9 @@
       <c r="L164" t="n">
         <v>900</v>
       </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -7693,6 +8197,9 @@
       <c r="L165" t="n">
         <v>840</v>
       </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -7737,6 +8244,9 @@
       <c r="L166" t="n">
         <v>600</v>
       </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -7781,6 +8291,9 @@
       <c r="L167" t="n">
         <v>1080</v>
       </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -7825,6 +8338,9 @@
       <c r="L168" t="n">
         <v>1080</v>
       </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -7869,6 +8385,9 @@
       <c r="L169" t="n">
         <v>1080</v>
       </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -7913,6 +8432,9 @@
       <c r="L170" t="n">
         <v>3240</v>
       </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -7957,6 +8479,9 @@
       <c r="L171" t="n">
         <v>1260</v>
       </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8001,6 +8526,9 @@
       <c r="L172" t="n">
         <v>2160</v>
       </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8045,6 +8573,9 @@
       <c r="L173" t="n">
         <v>840</v>
       </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8089,6 +8620,9 @@
       <c r="L174" t="n">
         <v>1260</v>
       </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8133,6 +8667,9 @@
       <c r="L175" t="n">
         <v>1080</v>
       </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8177,6 +8714,9 @@
       <c r="L176" t="n">
         <v>1080</v>
       </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8221,6 +8761,9 @@
       <c r="L177" t="n">
         <v>1200</v>
       </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8265,6 +8808,9 @@
       <c r="L178" t="n">
         <v>1260</v>
       </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8309,6 +8855,9 @@
       <c r="L179" t="n">
         <v>840</v>
       </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8353,6 +8902,9 @@
       <c r="L180" t="n">
         <v>1080</v>
       </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8397,6 +8949,9 @@
       <c r="L181" t="n">
         <v>960</v>
       </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8441,6 +8996,9 @@
       <c r="L182" t="n">
         <v>900</v>
       </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -8485,6 +9043,9 @@
       <c r="L183" t="n">
         <v>1800</v>
       </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -8529,6 +9090,9 @@
       <c r="L184" t="n">
         <v>1440</v>
       </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -8573,6 +9137,9 @@
       <c r="L185" t="n">
         <v>840</v>
       </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -8617,6 +9184,9 @@
       <c r="L186" t="n">
         <v>840</v>
       </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -8661,6 +9231,9 @@
       <c r="L187" t="n">
         <v>720</v>
       </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -8705,6 +9278,9 @@
       <c r="L188" t="n">
         <v>840</v>
       </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -8749,6 +9325,9 @@
       <c r="L189" t="n">
         <v>1080</v>
       </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -8793,6 +9372,9 @@
       <c r="L190" t="n">
         <v>1440</v>
       </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -8837,6 +9419,9 @@
       <c r="L191" t="n">
         <v>720</v>
       </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -8881,6 +9466,9 @@
       <c r="L192" t="n">
         <v>840</v>
       </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -8925,6 +9513,9 @@
       <c r="L193" t="n">
         <v>1440</v>
       </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -8969,6 +9560,9 @@
       <c r="L194" t="n">
         <v>1440</v>
       </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9013,6 +9607,9 @@
       <c r="L195" t="n">
         <v>960</v>
       </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9057,6 +9654,9 @@
       <c r="L196" t="n">
         <v>1200</v>
       </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9101,6 +9701,9 @@
       <c r="L197" t="n">
         <v>1980</v>
       </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9145,6 +9748,9 @@
       <c r="L198" t="n">
         <v>1440</v>
       </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9189,6 +9795,9 @@
       <c r="L199" t="n">
         <v>840</v>
       </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9233,6 +9842,9 @@
       <c r="L200" t="n">
         <v>1080</v>
       </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9277,6 +9889,9 @@
       <c r="L201" t="n">
         <v>1080</v>
       </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9321,6 +9936,9 @@
       <c r="L202" t="n">
         <v>2160</v>
       </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9365,6 +9983,9 @@
       <c r="L203" t="n">
         <v>840</v>
       </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9409,6 +10030,9 @@
       <c r="L204" t="n">
         <v>840</v>
       </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9453,6 +10077,9 @@
       <c r="L205" t="n">
         <v>1800</v>
       </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9497,6 +10124,9 @@
       <c r="L206" t="n">
         <v>1980</v>
       </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -9541,6 +10171,9 @@
       <c r="L207" t="n">
         <v>720</v>
       </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -9585,6 +10218,9 @@
       <c r="L208" t="n">
         <v>1800</v>
       </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -9629,6 +10265,9 @@
       <c r="L209" t="n">
         <v>1200</v>
       </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -9673,6 +10312,9 @@
       <c r="L210" t="n">
         <v>1260</v>
       </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -9717,6 +10359,9 @@
       <c r="L211" t="n">
         <v>1260</v>
       </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -9761,6 +10406,9 @@
       <c r="L212" t="n">
         <v>600</v>
       </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -9805,6 +10453,9 @@
       <c r="L213" t="n">
         <v>600</v>
       </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -9849,6 +10500,9 @@
       <c r="L214" t="n">
         <v>2640</v>
       </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -9893,6 +10547,9 @@
       <c r="L215" t="n">
         <v>840</v>
       </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -9937,6 +10594,9 @@
       <c r="L216" t="n">
         <v>1800</v>
       </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -9981,6 +10641,9 @@
       <c r="L217" t="n">
         <v>1200</v>
       </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10025,6 +10688,9 @@
       <c r="L218" t="n">
         <v>960</v>
       </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10069,6 +10735,9 @@
       <c r="L219" t="n">
         <v>1200</v>
       </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -10113,6 +10782,9 @@
       <c r="L220" t="n">
         <v>1440</v>
       </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10157,6 +10829,9 @@
       <c r="L221" t="n">
         <v>1560</v>
       </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10201,6 +10876,9 @@
       <c r="L222" t="n">
         <v>1440</v>
       </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10245,6 +10923,9 @@
       <c r="L223" t="n">
         <v>1200</v>
       </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10289,6 +10970,9 @@
       <c r="L224" t="n">
         <v>1080</v>
       </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -10333,6 +11017,9 @@
       <c r="L225" t="n">
         <v>600</v>
       </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10377,6 +11064,9 @@
       <c r="L226" t="n">
         <v>840</v>
       </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10421,6 +11111,9 @@
       <c r="L227" t="n">
         <v>2520</v>
       </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10465,6 +11158,9 @@
       <c r="L228" t="n">
         <v>960</v>
       </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10509,6 +11205,9 @@
       <c r="L229" t="n">
         <v>1440</v>
       </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10553,6 +11252,9 @@
       <c r="L230" t="n">
         <v>840</v>
       </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10597,6 +11299,9 @@
       <c r="L231" t="n">
         <v>1080</v>
       </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10641,6 +11346,9 @@
       <c r="L232" t="n">
         <v>1260</v>
       </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10685,6 +11393,9 @@
       <c r="L233" t="n">
         <v>1080</v>
       </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10729,6 +11440,9 @@
       <c r="L234" t="n">
         <v>720</v>
       </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10773,6 +11487,9 @@
       <c r="L235" t="n">
         <v>720</v>
       </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10817,6 +11534,9 @@
       <c r="L236" t="n">
         <v>840</v>
       </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10861,6 +11581,9 @@
       <c r="L237" t="n">
         <v>840</v>
       </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10905,6 +11628,9 @@
       <c r="L238" t="n">
         <v>1440</v>
       </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10949,6 +11675,9 @@
       <c r="L239" t="n">
         <v>1200</v>
       </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10993,6 +11722,9 @@
       <c r="L240" t="n">
         <v>1920</v>
       </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -11037,6 +11769,9 @@
       <c r="L241" t="n">
         <v>1080</v>
       </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -11081,6 +11816,9 @@
       <c r="L242" t="n">
         <v>600</v>
       </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -11125,6 +11863,9 @@
       <c r="L243" t="n">
         <v>3120</v>
       </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -11169,6 +11910,9 @@
       <c r="L244" t="n">
         <v>1260</v>
       </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11213,6 +11957,9 @@
       <c r="L245" t="n">
         <v>2160</v>
       </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -11257,6 +12004,9 @@
       <c r="L246" t="n">
         <v>2340</v>
       </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11301,6 +12051,9 @@
       <c r="L247" t="n">
         <v>840</v>
       </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11345,6 +12098,9 @@
       <c r="L248" t="n">
         <v>1260</v>
       </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -11389,6 +12145,9 @@
       <c r="L249" t="n">
         <v>1440</v>
       </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11433,6 +12192,9 @@
       <c r="L250" t="n">
         <v>1200</v>
       </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -11477,6 +12239,9 @@
       <c r="L251" t="n">
         <v>840</v>
       </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11521,6 +12286,9 @@
       <c r="L252" t="n">
         <v>1080</v>
       </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11565,6 +12333,9 @@
       <c r="L253" t="n">
         <v>1200</v>
       </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11609,6 +12380,9 @@
       <c r="L254" t="n">
         <v>600</v>
       </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11653,6 +12427,9 @@
       <c r="L255" t="n">
         <v>600</v>
       </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11697,6 +12474,9 @@
       <c r="L256" t="n">
         <v>1260</v>
       </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11741,6 +12521,9 @@
       <c r="L257" t="n">
         <v>1080</v>
       </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11785,6 +12568,9 @@
       <c r="L258" t="n">
         <v>360</v>
       </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11829,6 +12615,9 @@
       <c r="L259" t="n">
         <v>1920</v>
       </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11873,6 +12662,9 @@
       <c r="L260" t="n">
         <v>1200</v>
       </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11917,6 +12709,9 @@
       <c r="L261" t="n">
         <v>720</v>
       </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11961,6 +12756,9 @@
       <c r="L262" t="n">
         <v>600</v>
       </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -12005,6 +12803,9 @@
       <c r="L263" t="n">
         <v>840</v>
       </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -12049,6 +12850,9 @@
       <c r="L264" t="n">
         <v>1080</v>
       </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -12093,6 +12897,9 @@
       <c r="L265" t="n">
         <v>600</v>
       </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -12137,6 +12944,9 @@
       <c r="L266" t="n">
         <v>1620</v>
       </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -12181,6 +12991,9 @@
       <c r="L267" t="n">
         <v>1260</v>
       </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -12225,6 +13038,9 @@
       <c r="L268" t="n">
         <v>720</v>
       </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -12269,6 +13085,9 @@
       <c r="L269" t="n">
         <v>840</v>
       </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -12313,6 +13132,9 @@
       <c r="L270" t="n">
         <v>1080</v>
       </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -12357,6 +13179,9 @@
       <c r="L271" t="n">
         <v>600</v>
       </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -12401,6 +13226,9 @@
       <c r="L272" t="n">
         <v>1800</v>
       </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -12445,6 +13273,9 @@
       <c r="L273" t="n">
         <v>1080</v>
       </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -12489,6 +13320,9 @@
       <c r="L274" t="n">
         <v>720</v>
       </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -12533,6 +13367,9 @@
       <c r="L275" t="n">
         <v>1440</v>
       </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -12577,6 +13414,9 @@
       <c r="L276" t="n">
         <v>2160</v>
       </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -12621,6 +13461,9 @@
       <c r="L277" t="n">
         <v>840</v>
       </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -12665,6 +13508,9 @@
       <c r="L278" t="n">
         <v>600</v>
       </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -12709,6 +13555,9 @@
       <c r="L279" t="n">
         <v>1560</v>
       </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -12753,6 +13602,9 @@
       <c r="L280" t="n">
         <v>1440</v>
       </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -12797,6 +13649,9 @@
       <c r="L281" t="n">
         <v>1260</v>
       </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -12841,6 +13696,9 @@
       <c r="L282" t="n">
         <v>2160</v>
       </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -12885,6 +13743,9 @@
       <c r="L283" t="n">
         <v>1080</v>
       </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -12929,6 +13790,9 @@
       <c r="L284" t="n">
         <v>1200</v>
       </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -12973,6 +13837,9 @@
       <c r="L285" t="n">
         <v>1260</v>
       </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -13017,6 +13884,9 @@
       <c r="L286" t="n">
         <v>1200</v>
       </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -13061,6 +13931,9 @@
       <c r="L287" t="n">
         <v>840</v>
       </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -13105,6 +13978,9 @@
       <c r="L288" t="n">
         <v>1260</v>
       </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -13149,6 +14025,9 @@
       <c r="L289" t="n">
         <v>1800</v>
       </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -13193,6 +14072,9 @@
       <c r="L290" t="n">
         <v>1260</v>
       </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -13237,6 +14119,9 @@
       <c r="L291" t="n">
         <v>1800</v>
       </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -13281,6 +14166,9 @@
       <c r="L292" t="n">
         <v>840</v>
       </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -13325,6 +14213,9 @@
       <c r="L293" t="n">
         <v>840</v>
       </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -13369,6 +14260,9 @@
       <c r="L294" t="n">
         <v>1200</v>
       </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -13413,6 +14307,9 @@
       <c r="L295" t="n">
         <v>720</v>
       </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -13457,6 +14354,9 @@
       <c r="L296" t="n">
         <v>960</v>
       </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -13501,6 +14401,9 @@
       <c r="L297" t="n">
         <v>600</v>
       </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -13545,6 +14448,9 @@
       <c r="L298" t="n">
         <v>840</v>
       </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -13589,6 +14495,9 @@
       <c r="L299" t="n">
         <v>240</v>
       </c>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -13633,6 +14542,9 @@
       <c r="L300" t="n">
         <v>720</v>
       </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -13677,6 +14589,9 @@
       <c r="L301" t="n">
         <v>1620</v>
       </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -13721,6 +14636,9 @@
       <c r="L302" t="n">
         <v>1260</v>
       </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -13765,6 +14683,9 @@
       <c r="L303" t="n">
         <v>960</v>
       </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -13809,6 +14730,9 @@
       <c r="L304" t="n">
         <v>1080</v>
       </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -13853,6 +14777,9 @@
       <c r="L305" t="n">
         <v>1080</v>
       </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -13897,6 +14824,9 @@
       <c r="L306" t="n">
         <v>600</v>
       </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -13941,6 +14871,9 @@
       <c r="L307" t="n">
         <v>720</v>
       </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -13985,6 +14918,9 @@
       <c r="L308" t="n">
         <v>1080</v>
       </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -14029,6 +14965,9 @@
       <c r="L309" t="n">
         <v>900</v>
       </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -14073,6 +15012,9 @@
       <c r="L310" t="n">
         <v>1800</v>
       </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -14117,6 +15059,9 @@
       <c r="L311" t="n">
         <v>960</v>
       </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -14161,6 +15106,9 @@
       <c r="L312" t="n">
         <v>1080</v>
       </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -14205,6 +15153,9 @@
       <c r="L313" t="n">
         <v>720</v>
       </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -14249,6 +15200,9 @@
       <c r="L314" t="n">
         <v>840</v>
       </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -14293,6 +15247,9 @@
       <c r="L315" t="n">
         <v>1260</v>
       </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
+      <c r="O315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -14337,6 +15294,9 @@
       <c r="L316" t="n">
         <v>1260</v>
       </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -14381,6 +15341,9 @@
       <c r="L317" t="n">
         <v>1440</v>
       </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
+      <c r="O317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -14425,6 +15388,9 @@
       <c r="L318" t="n">
         <v>2340</v>
       </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -14469,6 +15435,9 @@
       <c r="L319" t="n">
         <v>2400</v>
       </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -14513,6 +15482,9 @@
       <c r="L320" t="n">
         <v>540</v>
       </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -14557,6 +15529,9 @@
       <c r="L321" t="n">
         <v>2280</v>
       </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -14601,6 +15576,9 @@
       <c r="L322" t="n">
         <v>480</v>
       </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -14645,6 +15623,9 @@
       <c r="L323" t="n">
         <v>600</v>
       </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -14689,6 +15670,9 @@
       <c r="L324" t="n">
         <v>1260</v>
       </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -14733,6 +15717,9 @@
       <c r="L325" t="n">
         <v>1080</v>
       </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -14777,6 +15764,9 @@
       <c r="L326" t="n">
         <v>840</v>
       </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -14821,6 +15811,9 @@
       <c r="L327" t="n">
         <v>900</v>
       </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -14865,6 +15858,9 @@
       <c r="L328" t="n">
         <v>840</v>
       </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -14909,6 +15905,9 @@
       <c r="L329" t="n">
         <v>1200</v>
       </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -14953,6 +15952,9 @@
       <c r="L330" t="n">
         <v>1200</v>
       </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -14997,6 +15999,9 @@
       <c r="L331" t="n">
         <v>1200</v>
       </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -15041,6 +16046,9 @@
       <c r="L332" t="n">
         <v>720</v>
       </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -15085,6 +16093,9 @@
       <c r="L333" t="n">
         <v>2160</v>
       </c>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -15129,6 +16140,9 @@
       <c r="L334" t="n">
         <v>2160</v>
       </c>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -15173,6 +16187,9 @@
       <c r="L335" t="n">
         <v>0</v>
       </c>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -15217,6 +16234,9 @@
       <c r="L336" t="n">
         <v>1800</v>
       </c>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -15261,6 +16281,9 @@
       <c r="L337" t="n">
         <v>1320</v>
       </c>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -15305,6 +16328,9 @@
       <c r="L338" t="n">
         <v>1080</v>
       </c>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -15349,6 +16375,9 @@
       <c r="L339" t="n">
         <v>2520</v>
       </c>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -15393,6 +16422,9 @@
       <c r="L340" t="n">
         <v>2160</v>
       </c>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -15437,6 +16469,9 @@
       <c r="L341" t="n">
         <v>1200</v>
       </c>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -15481,6 +16516,9 @@
       <c r="L342" t="n">
         <v>1680</v>
       </c>
+      <c r="M342" t="inlineStr"/>
+      <c r="N342" t="inlineStr"/>
+      <c r="O342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -15525,6 +16563,9 @@
       <c r="L343" t="n">
         <v>1080</v>
       </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -15569,6 +16610,9 @@
       <c r="L344" t="n">
         <v>720</v>
       </c>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -15613,6 +16657,9 @@
       <c r="L345" t="n">
         <v>1080</v>
       </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
+      <c r="O345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -15657,6 +16704,9 @@
       <c r="L346" t="n">
         <v>3240</v>
       </c>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -15701,6 +16751,9 @@
       <c r="L347" t="n">
         <v>2400</v>
       </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -15745,6 +16798,9 @@
       <c r="L348" t="n">
         <v>840</v>
       </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -15789,6 +16845,9 @@
       <c r="L349" t="n">
         <v>1200</v>
       </c>
+      <c r="M349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
+      <c r="O349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -15833,6 +16892,9 @@
       <c r="L350" t="n">
         <v>720</v>
       </c>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -15877,6 +16939,9 @@
       <c r="L351" t="n">
         <v>840</v>
       </c>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -15921,6 +16986,9 @@
       <c r="L352" t="n">
         <v>1440</v>
       </c>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -15965,6 +17033,9 @@
       <c r="L353" t="n">
         <v>1260</v>
       </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -16009,6 +17080,9 @@
       <c r="L354" t="n">
         <v>600</v>
       </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
+      <c r="O354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -16053,6 +17127,9 @@
       <c r="L355" t="n">
         <v>2160</v>
       </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -16097,6 +17174,9 @@
       <c r="L356" t="n">
         <v>960</v>
       </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -16141,6 +17221,9 @@
       <c r="L357" t="n">
         <v>1800</v>
       </c>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -16185,6 +17268,9 @@
       <c r="L358" t="n">
         <v>720</v>
       </c>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -16229,6 +17315,9 @@
       <c r="L359" t="n">
         <v>840</v>
       </c>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -16273,6 +17362,9 @@
       <c r="L360" t="n">
         <v>720</v>
       </c>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -16317,6 +17409,9 @@
       <c r="L361" t="n">
         <v>1800</v>
       </c>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -16361,6 +17456,9 @@
       <c r="L362" t="n">
         <v>1440</v>
       </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -16405,6 +17503,9 @@
       <c r="L363" t="n">
         <v>840</v>
       </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -16449,6 +17550,9 @@
       <c r="L364" t="n">
         <v>600</v>
       </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -16493,6 +17597,9 @@
       <c r="L365" t="n">
         <v>600</v>
       </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -16537,6 +17644,9 @@
       <c r="L366" t="n">
         <v>840</v>
       </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -16581,6 +17691,9 @@
       <c r="L367" t="n">
         <v>900</v>
       </c>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -16625,6 +17738,9 @@
       <c r="L368" t="n">
         <v>1260</v>
       </c>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -16669,6 +17785,9 @@
       <c r="L369" t="n">
         <v>2520</v>
       </c>
+      <c r="M369" t="inlineStr"/>
+      <c r="N369" t="inlineStr"/>
+      <c r="O369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -16713,6 +17832,9 @@
       <c r="L370" t="n">
         <v>720</v>
       </c>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -16757,6 +17879,9 @@
       <c r="L371" t="n">
         <v>540</v>
       </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -16801,6 +17926,9 @@
       <c r="L372" t="n">
         <v>900</v>
       </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -16845,6 +17973,9 @@
       <c r="L373" t="n">
         <v>960</v>
       </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -16889,6 +18020,9 @@
       <c r="L374" t="n">
         <v>1800</v>
       </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -16933,6 +18067,9 @@
       <c r="L375" t="n">
         <v>2160</v>
       </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -16977,6 +18114,9 @@
       <c r="L376" t="n">
         <v>600</v>
       </c>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -17021,6 +18161,9 @@
       <c r="L377" t="n">
         <v>600</v>
       </c>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="inlineStr"/>
+      <c r="O377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -17065,6 +18208,9 @@
       <c r="L378" t="n">
         <v>1800</v>
       </c>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+      <c r="O378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -17109,6 +18255,9 @@
       <c r="L379" t="n">
         <v>1080</v>
       </c>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -17153,6 +18302,9 @@
       <c r="L380" t="n">
         <v>960</v>
       </c>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -17197,6 +18349,9 @@
       <c r="L381" t="n">
         <v>1440</v>
       </c>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -17241,6 +18396,9 @@
       <c r="L382" t="n">
         <v>1080</v>
       </c>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -17285,6 +18443,9 @@
       <c r="L383" t="n">
         <v>1080</v>
       </c>
+      <c r="M383" t="inlineStr"/>
+      <c r="N383" t="inlineStr"/>
+      <c r="O383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -17329,6 +18490,9 @@
       <c r="L384" t="n">
         <v>1080</v>
       </c>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -17373,6 +18537,9 @@
       <c r="L385" t="n">
         <v>600</v>
       </c>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -17417,6 +18584,9 @@
       <c r="L386" t="n">
         <v>1260</v>
       </c>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -17461,6 +18631,9 @@
       <c r="L387" t="n">
         <v>840</v>
       </c>
+      <c r="M387" t="inlineStr"/>
+      <c r="N387" t="inlineStr"/>
+      <c r="O387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -17505,6 +18678,9 @@
       <c r="L388" t="n">
         <v>1260</v>
       </c>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -17549,6 +18725,9 @@
       <c r="L389" t="n">
         <v>1980</v>
       </c>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -17593,6 +18772,9 @@
       <c r="L390" t="n">
         <v>1080</v>
       </c>
+      <c r="M390" t="inlineStr"/>
+      <c r="N390" t="inlineStr"/>
+      <c r="O390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -17637,6 +18819,9 @@
       <c r="L391" t="n">
         <v>1200</v>
       </c>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -17681,6 +18866,9 @@
       <c r="L392" t="n">
         <v>600</v>
       </c>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -17725,6 +18913,9 @@
       <c r="L393" t="n">
         <v>900</v>
       </c>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr"/>
+      <c r="O393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -17769,6 +18960,9 @@
       <c r="L394" t="n">
         <v>1200</v>
       </c>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -17813,6 +19007,9 @@
       <c r="L395" t="n">
         <v>2160</v>
       </c>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -17857,6 +19054,9 @@
       <c r="L396" t="n">
         <v>840</v>
       </c>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -17901,6 +19101,9 @@
       <c r="L397" t="n">
         <v>1200</v>
       </c>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -17945,6 +19148,9 @@
       <c r="L398" t="n">
         <v>1080</v>
       </c>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr"/>
+      <c r="O398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -17989,6 +19195,9 @@
       <c r="L399" t="n">
         <v>1440</v>
       </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -18033,6 +19242,9 @@
       <c r="L400" t="n">
         <v>1260</v>
       </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -18077,12 +19289,13 @@
       <c r="L401" t="n">
         <v>1800</v>
       </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="A402" t="n">
+        <v>25</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -18115,16 +19328,37 @@
         </is>
       </c>
       <c r="H402" t="n">
-        <v>1283.45</v>
-      </c>
-      <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr"/>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L402" t="inlineStr"/>
+        <v>41769.27</v>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>S$ 2,380.00</t>
+        </is>
+      </c>
+      <c r="J402" t="n">
+        <v>120</v>
+      </c>
+      <c r="K402" t="n">
+        <v>5</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>S$ 600.00</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>S$ 2,140.00</t>
+        </is>
+      </c>
+      <c r="N402" t="n">
+        <v>200</v>
+      </c>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>S$ 40.00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
